--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/user-controller/deleteAdmin-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/user-controller/deleteAdmin-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="53">
   <si>
     <t>Statement: deleteAdmin(adminId: string): Promise&lt;ActionResult&lt;void&gt;&gt; — delegates to userService.deleteAdmin() and returns a void ActionResult on success.</t>
   </si>
@@ -119,6 +119,17 @@
   </si>
   <si>
     <t>No change</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One admin seeded via userService.createAdmin().
+First call: deleteAdmin("00000000-0000-0000-0000-000000000000") → NotFoundError.
+const id: string = seeded.id</t>
+  </si>
+  <si>
+    <t>Seeded admin row absent; no other rows affected</t>
   </si>
   <si>
     <t>Testing</t>
@@ -803,7 +814,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -903,6 +914,29 @@
         <v>33</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -931,17 +965,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -953,40 +987,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -994,40 +1028,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
